--- a/PRIMER PARCIAL/TALLERES/GN6_Matriz_IREB_VNº_6.xlsx
+++ b/PRIMER PARCIAL/TALLERES/GN6_Matriz_IREB_VNº_6.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="124">
   <si>
     <t>MATRIZ PARA COMPROBACIÓN REQUERIMIENTOS DE CALIDAD DE PROYECTO ACADEMICO</t>
   </si>
@@ -52,13 +52,13 @@
   </si>
   <si>
     <t xml:space="preserve">
-CU-01: Administrar Sistema (Nivel 0)</t>
-  </si>
-  <si>
-    <t>CU-1.1: Iniciar Sesión (Expandido)</t>
-  </si>
-  <si>
-    <t>CU-1.2: Recuperar Contraseña (Expandido)</t>
+CU-01: Administrar Sistema</t>
+  </si>
+  <si>
+    <t>CU-1.1: Iniciar Sesión</t>
+  </si>
+  <si>
+    <t>CU-1.2: Recuperar Contraseña</t>
   </si>
   <si>
     <t>Agreed</t>
@@ -94,7 +94,10 @@
     <t>Define claramente que gestiona acceso, autenticación y perfiles.</t>
   </si>
   <si>
-    <t>Especifica formatos (alfanumérico, 3-20 caracteres).</t>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>No se especifica si el bloqueo de cuenta es por IP o por ID de usuario, lo que genera ambigüedad en la política de seguridad.</t>
   </si>
   <si>
     <t>Define que el código es de 6 dígitos y dura 10 minutos.</t>
@@ -133,7 +136,7 @@
     <t>Se alinea con el RNF-01 (bcrypt y bloqueo de cuenta).</t>
   </si>
   <si>
-    <t>Coincide con las reglas de seguridad de contraseñas (min 8 caracteres, etc.).</t>
+    <t>Existe una inconsistencia sobre el estado de las sesiones activas en otros dispositivos al momento de cambiar la contraseña.</t>
   </si>
   <si>
     <t>Verifiable</t>
@@ -142,7 +145,7 @@
     <t>Se verifica mediante pruebas de caja negra (login exitoso/fallido).</t>
   </si>
   <si>
-    <t>Cambia a OK: Se puede probar el bloqueo tras el 3er intento fallido.</t>
+    <t>El criterio de "bloqueo de 15 min" no es verificable sin definir si el contador se reinicia ante cada intento fallido adicional durante el bloqueo.</t>
   </si>
   <si>
     <t>Se puede verificar enviando el correo y validando el código en el sistema.</t>
@@ -157,7 +160,7 @@
     <t>Cambia a OK: Factible mediante el uso de bases de datos y manejo de sesiones.</t>
   </si>
   <si>
-    <t>Requiere un servicio de SMTP (correo), común en proyectos web.</t>
+    <t>La factibilidad técnica depende de un servicio SMTP externo cuya latencia no ha sido considerada en los tiempos de respuesta del RNF-05.</t>
   </si>
   <si>
     <t>Traceable</t>
@@ -181,13 +184,13 @@
     <t>Tiene precondiciones, postcondiciones y manejo de excepciones (flujo alterno).</t>
   </si>
   <si>
-    <t>Incluye flujos de error para códigos expirados o correos inexistentes.</t>
+    <t>El flujo no describe qué sucede si el usuario solicita un nuevo código antes de que expire el anterior (solapamiento de tokens).</t>
   </si>
   <si>
     <t>Understandability</t>
   </si>
   <si>
-    <t>El lenguaje es claro tanto para el cliente como para el equipo técnico.</t>
+    <t>No define el flujo de "Cierre de Sesión" (Logout), dejando incompleto el ciclo de vida de la administración de acceso.</t>
   </si>
   <si>
     <t>Detalla el proceso de validación paso a paso.</t>
@@ -202,13 +205,13 @@
     <t>AUTOR:</t>
   </si>
   <si>
-    <t>Stiven Diaz, Jose Leiton, Gabriel Manosalvas</t>
+    <t>Jose Leiton</t>
   </si>
   <si>
     <t>REQUERIMIENTOS EVALUADOS :</t>
   </si>
   <si>
-    <t>CU001 - CU002 - CU003</t>
+    <t>CU-01</t>
   </si>
   <si>
     <t>CONTENIDO</t>
@@ -298,6 +301,35 @@
     <t xml:space="preserve">CONTENIDO </t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="14.0"/>
+      </rPr>
+      <t xml:space="preserve">AUTOR:  </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b val="0"/>
+        <color theme="1"/>
+        <sz val="14.0"/>
+      </rPr>
+      <t>Stiven Díaz</t>
+    </r>
+  </si>
+  <si>
+    <t>CU-1.1</t>
+  </si>
+  <si>
+    <t>Gabriel Manosalvas</t>
+  </si>
+  <si>
+    <t>CU-1.2</t>
+  </si>
+  <si>
     <t>PREGUNTA</t>
   </si>
   <si>
@@ -338,13 +370,64 @@
   </si>
   <si>
     <t>Definir una excepción clara en el RF-1.2 que indique al usuario: "Servicio de correo temporalmente fuera de línea, intente más tarde", evitando que el sistema se quede "pensando" o muestre un error técnico (500) que confunda al copropietario.</t>
+  </si>
+  <si>
+    <t>CU - 1.1</t>
+  </si>
+  <si>
+    <t>¿Cómo avisa el sistema cuando la sesión caduca?</t>
+  </si>
+  <si>
+    <t>Los comentarios indican que la sesión expira a las 2 horas. Se recomienda detallar en el flujo que el sistema debe devolver al usuario a la pantalla de inicio mostrando un mensaje claro: "Su sesión ha expirado por inactividad. Ingrese nuevamente"</t>
+  </si>
+  <si>
+    <t>¿El usuario distingue entre mayúsculas y minúsculas?</t>
+  </si>
+  <si>
+    <t>Para evitar bloqueos tontos si el copropietario escribe "CASA15" en lugar de "casa15", se recomienda especificar en el paso 2 del flujo normal  que el sistema transforma todo a minúsculas antes de validar (case-insensitive).</t>
+  </si>
+  <si>
+    <t>Cuándo se reinicia el contador de intentos fallidos?</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la cuenta al tercer intento malo. Se recomienda añadir una nota que aclare que si el usuario se equivoca 2 veces, pero a la tercera ingresa correctamente, el contador de errores vuelve a cero automáticamente.</t>
+  </si>
+  <si>
+    <t>¿Qué pasa visualmente si deja campos vacíos?</t>
+  </si>
+  <si>
+    <t>Alineado con el RNF-06 de usabilidad , se recomienda indicar en el paso 2  que si el usuario no pone la clave, el campo se marque en rojo advirtiendo el error inmediatamente, sin tener que recargar la página</t>
+  </si>
+  <si>
+    <t>¿Qué pasa con las sesiones abiertas en otros equipos tras cambiar la clave?</t>
+  </si>
+  <si>
+    <t>Indicar en la postcondición que, al cambiar la contraseña con éxito, el sistema cierra automáticamente la sesión en cualquier otro dispositivo activo (móvil, PC) por seguridad.</t>
+  </si>
+  <si>
+    <t>¿Qué ocurre si el correo tarda en enviarse por culpa del servidor?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Especificar que el sistema debe mostrar un estado de "Enviando..." y, si el correo falla, mostrar un mensaje amigable como "El servicio de correo está tardando, intente más tarde", para justificar los tiempos del RNF-05</t>
+  </si>
+  <si>
+    <t>¿El sistema anula el código anterior si el usuario se desespera y pide otro?</t>
+  </si>
+  <si>
+    <t>Añadir en el flujo normal que si el usuario solicita un nuevo código antes de los 10 minutos, el código anterior caduca inmediatamente para evitar confusiones de "solapamiento".</t>
+  </si>
+  <si>
+    <t>¿Se unificaron los identificadores en todo el documento?</t>
+  </si>
+  <si>
+    <t>Corregir el ID en la Matriz de Priorización, ya que actualmente figura como "RF-02" cuando pertenece a "RF-1.2". Esto arregla inmediatamente la trazabilidad.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -430,7 +513,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -438,8 +521,20 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,8 +561,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB8CCE4"/>
         <bgColor rgb="FFB8CCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor rgb="FF9BBB59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF1DD"/>
+        <bgColor rgb="FFEAF1DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+        <bgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor rgb="FFFDE9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -634,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="106">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -690,6 +821,9 @@
     <xf borderId="9" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -717,13 +851,13 @@
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -773,7 +907,146 @@
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="11" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="14" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="4" fillId="12" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -783,6 +1056,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -923,7 +1202,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="3">
+  <tableStyles count="9">
     <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -935,6 +1214,36 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 3">
+      <tableStyleElement dxfId="6" type="headerRow"/>
+      <tableStyleElement dxfId="7" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 4">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 5">
+      <tableStyleElement dxfId="4" type="headerRow"/>
+      <tableStyleElement dxfId="5" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 6">
+      <tableStyleElement dxfId="6" type="headerRow"/>
+      <tableStyleElement dxfId="7" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 7">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 8">
+      <tableStyleElement dxfId="4" type="headerRow"/>
+      <tableStyleElement dxfId="5" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 9">
       <tableStyleElement dxfId="6" type="headerRow"/>
       <tableStyleElement dxfId="7" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -1071,6 +1380,262 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>CRITERIO DE CALIDAD </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3094930008748907"/>
+          <c:y val="0.06018518518518518"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:perspective val="0"/>
+    </c:view3D>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4F81BD"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'MODELO LISTA DE COMPROBACION - '!$B$85:$B$87</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MODELO LISTA DE COMPROBACION - '!$C$85:$C$87</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="757575"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>CRITERIO DE CALIDAD </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3094930008748907"/>
+          <c:y val="0.06018518518518518"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:perspective val="0"/>
+    </c:view3D>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4F81BD"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'MODELO LISTA DE COMPROBACION - '!$B$85:$B$87</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MODELO LISTA DE COMPROBACION - '!$C$129:$C$131</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -1097,6 +1662,56 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>276225</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4286250" cy="2143125"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4286250" cy="2143125"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3" title="Gráfico"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1146,6 +1761,78 @@
     <tableColumn name="NO " id="4"/>
   </tableColumns>
   <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A51:D60" displayName="Table_4" name="Table_4" id="4">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A65:D70" displayName="Table_5" name="Table_5" id="5">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 5" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A75:D78" displayName="Table_6" name="Table_6" id="6">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 6" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A95:D104" displayName="Table_7" name="Table_7" id="7">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 7" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A109:D114" displayName="Table_8" name="Table_8" id="8">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 8" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A119:D122" displayName="Table_9" name="Table_9" id="9">
+  <tableColumns count="4">
+    <tableColumn name="No." id="1"/>
+    <tableColumn name="Pregunta" id="2"/>
+    <tableColumn name="SI" id="3"/>
+    <tableColumn name="NO " id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 9" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1478,7 +2165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1">
+    <row r="11" ht="50.25" customHeight="1">
       <c r="B11" s="14">
         <v>3.0</v>
       </c>
@@ -1492,17 +2179,17 @@
       <c r="F11" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>10</v>
+      <c r="G11" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="20" t="s">
         <v>10</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1">
@@ -1510,26 +2197,26 @@
         <v>4.0</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>23</v>
+      <c r="F12" s="24" t="s">
+        <v>24</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>24</v>
+      <c r="I12" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="J12" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="23" t="s">
-        <v>25</v>
+      <c r="K12" s="24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="29.25" customHeight="1">
@@ -1537,53 +2224,53 @@
         <v>5.0</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="23" t="s">
-        <v>27</v>
+      <c r="F13" s="24" t="s">
+        <v>28</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="23" t="s">
-        <v>28</v>
+      <c r="I13" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" ht="29.25" customHeight="1">
+      <c r="K13" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="60.0" customHeight="1">
       <c r="B14" s="14">
         <v>6.0</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="F14" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="23" t="s">
+      <c r="I14" s="24" t="s">
         <v>33</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -1591,53 +2278,53 @@
         <v>7.0</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="16"/>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="23" t="s">
+      <c r="F15" s="24" t="s">
         <v>36</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>37</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" ht="35.25" customHeight="1">
+      <c r="K15" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="14">
         <v>8.0</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>39</v>
+      <c r="F16" s="24" t="s">
+        <v>40</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="K16" s="23" t="s">
+      <c r="I16" s="24" t="s">
         <v>41</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
@@ -1645,26 +2332,26 @@
         <v>9.0</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="24" t="s">
-        <v>43</v>
+      <c r="F17" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="24" t="s">
-        <v>44</v>
+      <c r="I17" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>45</v>
+      <c r="K17" s="25" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -1672,53 +2359,53 @@
         <v>10.0</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="16"/>
-      <c r="E18" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>47</v>
+      <c r="E18" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I18" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="K18" s="23" t="s">
+      <c r="I18" s="24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" ht="33.75" customHeight="1">
+      <c r="J18" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
       <c r="B19" s="14">
         <v>11.0</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="23" t="s">
-        <v>51</v>
+      <c r="F19" s="24" t="s">
+        <v>52</v>
       </c>
       <c r="G19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>52</v>
+      <c r="I19" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K19" s="23" t="s">
-        <v>53</v>
+      <c r="K19" s="24" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -3106,27 +3793,27 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G7:G8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
     <mergeCell ref="C3:K4"/>
     <mergeCell ref="E5:K5"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C7:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.7480314960629921" footer="0.0" header="0.0" left="0.47" right="0.7086614173228347" top="0.7480314960629921"/>
@@ -3153,191 +3840,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="26"/>
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
     </row>
     <row r="2" ht="52.5" customHeight="1">
-      <c r="B2" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="29">
+      <c r="B2" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="30">
         <v>46126.0</v>
       </c>
     </row>
     <row r="3" ht="38.25" customHeight="1">
-      <c r="B3" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>56</v>
       </c>
+      <c r="C3" s="31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="4" ht="41.25" customHeight="1">
-      <c r="B4" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>58</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>59</v>
+      <c r="A6" s="32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="33" t="s">
+      <c r="A7" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="C7" s="34" t="s">
         <v>63</v>
       </c>
+      <c r="D7" s="35" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="35">
+      <c r="A8" s="36">
         <v>1.0</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="37" t="s">
+      <c r="B8" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="38"/>
+      <c r="C8" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="39"/>
     </row>
     <row r="9" ht="26.25" customHeight="1">
-      <c r="A9" s="35">
+      <c r="A9" s="36">
         <v>2.0</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="38"/>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="35">
+      <c r="A10" s="36">
         <v>3.0</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="38"/>
+      <c r="B10" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" ht="28.5" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="36">
         <v>4.0</v>
       </c>
-      <c r="B11" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="38"/>
+      <c r="B11" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="35">
+      <c r="A12" s="36">
         <v>5.0</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="38"/>
+      <c r="B12" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" ht="26.25" customHeight="1">
-      <c r="A13" s="35">
+      <c r="A13" s="36">
         <v>6.0</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="38"/>
+      <c r="B13" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" ht="27.0" customHeight="1">
-      <c r="A14" s="35">
+      <c r="A14" s="36">
         <v>7.0</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="38"/>
+      <c r="B14" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" ht="29.25" customHeight="1">
-      <c r="A15" s="35">
+      <c r="A15" s="36">
         <v>8.0</v>
       </c>
-      <c r="B15" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="38"/>
+      <c r="B15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="39"/>
     </row>
     <row r="16" ht="57.75" customHeight="1">
-      <c r="A16" s="39">
+      <c r="A16" s="40">
         <v>9.0</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41" t="s">
-        <v>65</v>
+      <c r="B16" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="42" t="s">
-        <v>74</v>
+      <c r="A17" s="43" t="s">
+        <v>75</v>
       </c>
       <c r="C17" s="19">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$8:$C$16)</f>
@@ -3349,109 +4036,109 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="43">
+      <c r="A18" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="44">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
         <v>0.8888888889</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <f t="shared" si="1"/>
         <v>0.1111111111</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="19"/>
     </row>
     <row r="20" ht="24.75" customHeight="1">
-      <c r="A20" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
+      <c r="A20" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
     </row>
     <row r="21" ht="21.75" customHeight="1">
-      <c r="A21" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="47" t="s">
+      <c r="A21" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="B21" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="C21" s="49" t="s">
         <v>63</v>
       </c>
+      <c r="D21" s="50" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="35">
+      <c r="A22" s="36">
         <v>1.0</v>
       </c>
-      <c r="B22" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="38"/>
+      <c r="B22" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="39"/>
     </row>
     <row r="23" ht="28.5" customHeight="1">
-      <c r="A23" s="35">
+      <c r="A23" s="36">
         <v>2.0</v>
       </c>
-      <c r="B23" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="38"/>
+      <c r="B23" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="39"/>
     </row>
     <row r="24" ht="21.0" customHeight="1">
-      <c r="A24" s="35">
+      <c r="A24" s="36">
         <v>3.0</v>
       </c>
-      <c r="B24" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="38"/>
+      <c r="B24" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="39"/>
     </row>
     <row r="25" ht="32.25" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="36">
         <v>4.0</v>
       </c>
-      <c r="B25" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="38"/>
+      <c r="B25" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="39"/>
     </row>
     <row r="26" ht="21.0" customHeight="1">
-      <c r="A26" s="39">
+      <c r="A26" s="40">
         <v>5.0</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="50"/>
+      <c r="B26" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="51"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="42" t="s">
-        <v>74</v>
+      <c r="A27" s="43" t="s">
+        <v>75</v>
       </c>
       <c r="C27" s="19">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$22:$C$26)</f>
@@ -3463,82 +4150,82 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="43">
+      <c r="A28" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="44">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="43">
+      <c r="D28" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
       <c r="D29" s="19"/>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>82</v>
+      <c r="A30" s="32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" ht="20.25" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="47" t="s">
+      <c r="A31" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="B31" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="C31" s="49" t="s">
         <v>63</v>
       </c>
+      <c r="D31" s="50" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="32" ht="30.75" customHeight="1">
-      <c r="A32" s="35">
+      <c r="A32" s="36">
         <v>1.0</v>
       </c>
-      <c r="B32" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="41"/>
+      <c r="B32" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="42"/>
     </row>
     <row r="33" ht="30.75" customHeight="1">
-      <c r="A33" s="35">
+      <c r="A33" s="36">
         <v>2.0</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="41"/>
+      <c r="B33" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="42"/>
     </row>
     <row r="34" ht="30.0" customHeight="1">
-      <c r="A34" s="39">
+      <c r="A34" s="40">
         <v>3.0</v>
       </c>
-      <c r="B34" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="41"/>
+      <c r="B34" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="42"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="42" t="s">
-        <v>74</v>
+      <c r="A35" s="43" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="19">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$32:$C$34)</f>
@@ -3550,14 +4237,14 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="43">
+      <c r="A36" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="44">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
         <v>1</v>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3566,29 +4253,29 @@
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="51" t="s">
-        <v>86</v>
+      <c r="A40" s="52" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="25" t="s">
-        <v>87</v>
+      <c r="B41" s="26" t="s">
+        <v>88</v>
       </c>
       <c r="C41" s="19">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="25" t="s">
-        <v>76</v>
+      <c r="B42" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="C42" s="19">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="25" t="s">
-        <v>82</v>
+      <c r="B43" s="26" t="s">
+        <v>83</v>
       </c>
       <c r="C43" s="19">
         <v>100.0</v>
@@ -3600,98 +4287,1251 @@
     <row r="45" ht="14.25" customHeight="1">
       <c r="C45" s="19"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="C46" s="19"/>
+    </row>
+    <row r="47" ht="38.25" customHeight="1">
+      <c r="B47" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="31"/>
+    </row>
+    <row r="48" ht="41.25" customHeight="1">
+      <c r="B48" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>90</v>
+      </c>
+    </row>
     <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="50" ht="18.0" customHeight="1">
+      <c r="A50" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" ht="15.0" customHeight="1">
+      <c r="A51" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" ht="30.75" customHeight="1">
+      <c r="A52" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="B52" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="39"/>
+    </row>
+    <row r="53" ht="26.25" customHeight="1">
+      <c r="A53" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="B53" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" ht="30.0" customHeight="1">
+      <c r="A54" s="36">
+        <v>3.0</v>
+      </c>
+      <c r="B54" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" ht="28.5" customHeight="1">
+      <c r="A55" s="36">
+        <v>4.0</v>
+      </c>
+      <c r="B55" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="39"/>
+    </row>
+    <row r="56" ht="36.75" customHeight="1">
+      <c r="A56" s="36">
+        <v>5.0</v>
+      </c>
+      <c r="B56" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="39"/>
+    </row>
+    <row r="57" ht="26.25" customHeight="1">
+      <c r="A57" s="36">
+        <v>6.0</v>
+      </c>
+      <c r="B57" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="39"/>
+    </row>
+    <row r="58" ht="27.0" customHeight="1">
+      <c r="A58" s="36">
+        <v>7.0</v>
+      </c>
+      <c r="B58" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" ht="29.25" customHeight="1">
+      <c r="A59" s="36">
+        <v>8.0</v>
+      </c>
+      <c r="B59" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="39"/>
+    </row>
+    <row r="60" ht="57.75" customHeight="1">
+      <c r="A60" s="40">
+        <v>9.0</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1">
+      <c r="A61" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="54">
+        <v>6.0</v>
+      </c>
+      <c r="D61" s="54">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" customHeight="1">
+      <c r="A62" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="44">
+        <f t="shared" ref="C62:D62" si="4">C61/9</f>
+        <v>0.6666666667</v>
+      </c>
+      <c r="D62" s="44">
+        <f t="shared" si="4"/>
+        <v>0.3333333333</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" customHeight="1">
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="19"/>
+    </row>
+    <row r="64" ht="24.75" customHeight="1">
+      <c r="A64" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+    </row>
+    <row r="65" ht="21.75" customHeight="1">
+      <c r="A65" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" ht="32.25" customHeight="1">
+      <c r="A66" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="B66" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66" s="39"/>
+    </row>
+    <row r="67" ht="28.5" customHeight="1">
+      <c r="A67" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="B67" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="39"/>
+    </row>
+    <row r="68" ht="21.0" customHeight="1">
+      <c r="A68" s="36">
+        <v>3.0</v>
+      </c>
+      <c r="B68" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="39"/>
+    </row>
+    <row r="69" ht="32.25" customHeight="1">
+      <c r="A69" s="36">
+        <v>4.0</v>
+      </c>
+      <c r="B69" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D69" s="39"/>
+    </row>
+    <row r="70" ht="21.0" customHeight="1">
+      <c r="A70" s="40">
+        <v>5.0</v>
+      </c>
+      <c r="B70" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="51"/>
+    </row>
+    <row r="71" ht="14.25" customHeight="1">
+      <c r="A71" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="19">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$22:$C$26)</f>
+        <v>5</v>
+      </c>
+      <c r="D71" s="19">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$22:$D$26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25" customHeight="1">
+      <c r="A72" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="44">
+        <f t="shared" ref="C72:D72" si="5">C71/5</f>
+        <v>1</v>
+      </c>
+      <c r="D72" s="44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" customHeight="1">
+      <c r="A73" s="43"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="19"/>
+    </row>
+    <row r="74" ht="20.25" customHeight="1">
+      <c r="A74" s="32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" ht="20.25" customHeight="1">
+      <c r="A75" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D75" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" ht="30.75" customHeight="1">
+      <c r="A76" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="42"/>
+    </row>
+    <row r="77" ht="30.75" customHeight="1">
+      <c r="A77" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="B77" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" s="42"/>
+    </row>
+    <row r="78" ht="30.0" customHeight="1">
+      <c r="A78" s="40">
+        <v>3.0</v>
+      </c>
+      <c r="B78" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D78" s="42"/>
+    </row>
+    <row r="79" ht="14.25" customHeight="1">
+      <c r="A79" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="19">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$32:$C$34)</f>
+        <v>3</v>
+      </c>
+      <c r="D79" s="19">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$32:$D$34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="14.25" customHeight="1">
+      <c r="A80" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C80" s="44">
+        <f t="shared" ref="C80:D80" si="6">C79/3</f>
+        <v>1</v>
+      </c>
+      <c r="D80" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="81" ht="14.25" customHeight="1"/>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1">
+      <c r="A84" s="52" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" ht="30.0" customHeight="1">
+      <c r="B85" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="54">
+        <v>67.0</v>
+      </c>
+    </row>
+    <row r="86" ht="30.0" customHeight="1">
+      <c r="B86" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" s="19">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="87" ht="30.0" customHeight="1">
+      <c r="B87" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" s="19">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="C88" s="19"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="C89" s="19"/>
+    </row>
     <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1">
+      <c r="A91" s="55"/>
+      <c r="B91" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="55"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="55"/>
+      <c r="I91" s="55"/>
+      <c r="J91" s="55"/>
+      <c r="K91" s="55"/>
+      <c r="L91" s="55"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="55"/>
+      <c r="B92" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C92" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
+      <c r="L92" s="55"/>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="A93" s="55"/>
+      <c r="B93" s="55"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
+      <c r="L93" s="55"/>
+    </row>
+    <row r="94" ht="23.25" customHeight="1">
+      <c r="A94" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
+      <c r="L94" s="55"/>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D95" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
+      <c r="L95" s="55"/>
+    </row>
+    <row r="96" ht="35.25" customHeight="1">
+      <c r="A96" s="63">
+        <v>1.0</v>
+      </c>
+      <c r="B96" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C96" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D96" s="66"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
+      <c r="L96" s="55"/>
+    </row>
+    <row r="97" ht="29.25" customHeight="1">
+      <c r="A97" s="67">
+        <v>2.0</v>
+      </c>
+      <c r="B97" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" s="69"/>
+      <c r="D97" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
+      <c r="L97" s="55"/>
+    </row>
+    <row r="98" ht="54.0" customHeight="1">
+      <c r="A98" s="63">
+        <v>3.0</v>
+      </c>
+      <c r="B98" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C98" s="71"/>
+      <c r="D98" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
+      <c r="L98" s="55"/>
+    </row>
+    <row r="99" ht="28.5" customHeight="1">
+      <c r="A99" s="67">
+        <v>4.0</v>
+      </c>
+      <c r="B99" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C99" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D99" s="72"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="55"/>
+      <c r="L99" s="55"/>
+    </row>
+    <row r="100" ht="26.25" customHeight="1">
+      <c r="A100" s="63">
+        <v>5.0</v>
+      </c>
+      <c r="B100" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D100" s="71"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
+      <c r="I100" s="55"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="55"/>
+      <c r="L100" s="55"/>
+    </row>
+    <row r="101" ht="28.5" customHeight="1">
+      <c r="A101" s="67">
+        <v>6.0</v>
+      </c>
+      <c r="B101" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="C101" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D101" s="72"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="55"/>
+      <c r="H101" s="55"/>
+      <c r="I101" s="55"/>
+      <c r="J101" s="55"/>
+      <c r="K101" s="55"/>
+      <c r="L101" s="55"/>
+    </row>
+    <row r="102" ht="30.75" customHeight="1">
+      <c r="A102" s="63">
+        <v>7.0</v>
+      </c>
+      <c r="B102" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" s="71"/>
+      <c r="D102" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="E102" s="55"/>
+      <c r="F102" s="55"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="55"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="55"/>
+      <c r="L102" s="55"/>
+    </row>
+    <row r="103" ht="30.75" customHeight="1">
+      <c r="A103" s="67">
+        <v>8.0</v>
+      </c>
+      <c r="B103" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D103" s="72"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="55"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="55"/>
+      <c r="J103" s="55"/>
+      <c r="K103" s="55"/>
+      <c r="L103" s="55"/>
+    </row>
+    <row r="104" ht="54.0" customHeight="1">
+      <c r="A104" s="73">
+        <v>9.0</v>
+      </c>
+      <c r="B104" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C104" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D104" s="69"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="55"/>
+      <c r="I104" s="55"/>
+      <c r="J104" s="55"/>
+      <c r="K104" s="55"/>
+      <c r="L104" s="55"/>
+    </row>
+    <row r="105" ht="14.25" customHeight="1">
+      <c r="A105" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C105" s="75">
+        <v>6.0</v>
+      </c>
+      <c r="D105" s="75">
+        <v>3.0</v>
+      </c>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="55"/>
+      <c r="J105" s="55"/>
+      <c r="K105" s="55"/>
+      <c r="L105" s="55"/>
+    </row>
+    <row r="106" ht="14.25" customHeight="1">
+      <c r="A106" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C106" s="76">
+        <f t="shared" ref="C106:D106" si="7">C105/9</f>
+        <v>0.6666666667</v>
+      </c>
+      <c r="D106" s="76">
+        <f t="shared" si="7"/>
+        <v>0.3333333333</v>
+      </c>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55"/>
+      <c r="J106" s="55"/>
+      <c r="K106" s="55"/>
+      <c r="L106" s="55"/>
+    </row>
+    <row r="107" ht="14.25" customHeight="1">
+      <c r="A107" s="55"/>
+      <c r="B107" s="55"/>
+      <c r="C107" s="77"/>
+      <c r="D107" s="55"/>
+      <c r="E107" s="55"/>
+      <c r="F107" s="55"/>
+      <c r="G107" s="55"/>
+      <c r="H107" s="55"/>
+      <c r="I107" s="55"/>
+      <c r="J107" s="55"/>
+      <c r="K107" s="55"/>
+      <c r="L107" s="55"/>
+    </row>
+    <row r="108" ht="36.0" customHeight="1">
+      <c r="A108" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B108" s="46"/>
+      <c r="C108" s="46"/>
+      <c r="D108" s="46"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="55"/>
+      <c r="H108" s="55"/>
+      <c r="I108" s="55"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="55"/>
+      <c r="L108" s="55"/>
+    </row>
+    <row r="109" ht="14.25" customHeight="1">
+      <c r="A109" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="B109" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="C109" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="D109" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="E109" s="55"/>
+      <c r="F109" s="55"/>
+      <c r="G109" s="55"/>
+      <c r="H109" s="55"/>
+      <c r="I109" s="55"/>
+      <c r="J109" s="55"/>
+      <c r="K109" s="55"/>
+      <c r="L109" s="55"/>
+    </row>
+    <row r="110" ht="32.25" customHeight="1">
+      <c r="A110" s="83">
+        <v>1.0</v>
+      </c>
+      <c r="B110" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="C110" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" s="86"/>
+      <c r="E110" s="55"/>
+      <c r="F110" s="55"/>
+      <c r="G110" s="55"/>
+      <c r="H110" s="55"/>
+      <c r="I110" s="55"/>
+      <c r="J110" s="55"/>
+      <c r="K110" s="55"/>
+      <c r="L110" s="55"/>
+    </row>
+    <row r="111" ht="30.0" customHeight="1">
+      <c r="A111" s="87">
+        <v>2.0</v>
+      </c>
+      <c r="B111" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C111" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D111" s="72"/>
+      <c r="E111" s="55"/>
+      <c r="F111" s="55"/>
+      <c r="G111" s="55"/>
+      <c r="H111" s="55"/>
+      <c r="I111" s="55"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="55"/>
+      <c r="L111" s="55"/>
+    </row>
+    <row r="112" ht="32.25" customHeight="1">
+      <c r="A112" s="83">
+        <v>3.0</v>
+      </c>
+      <c r="B112" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="C112" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="D112" s="86"/>
+      <c r="E112" s="55"/>
+      <c r="F112" s="55"/>
+      <c r="G112" s="55"/>
+      <c r="H112" s="55"/>
+      <c r="I112" s="55"/>
+      <c r="J112" s="55"/>
+      <c r="K112" s="55"/>
+      <c r="L112" s="55"/>
+    </row>
+    <row r="113" ht="27.75" customHeight="1">
+      <c r="A113" s="87">
+        <v>4.0</v>
+      </c>
+      <c r="B113" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C113" s="69"/>
+      <c r="D113" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E113" s="55"/>
+      <c r="F113" s="55"/>
+      <c r="G113" s="55"/>
+      <c r="H113" s="55"/>
+      <c r="I113" s="55"/>
+      <c r="J113" s="55"/>
+      <c r="K113" s="55"/>
+      <c r="L113" s="55"/>
+    </row>
+    <row r="114" ht="23.25" customHeight="1">
+      <c r="A114" s="83">
+        <v>5.0</v>
+      </c>
+      <c r="B114" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="C114" s="85"/>
+      <c r="D114" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="E114" s="55"/>
+      <c r="F114" s="55"/>
+      <c r="G114" s="55"/>
+      <c r="H114" s="55"/>
+      <c r="I114" s="55"/>
+      <c r="J114" s="55"/>
+      <c r="K114" s="55"/>
+      <c r="L114" s="55"/>
+    </row>
+    <row r="115" ht="14.25" customHeight="1">
+      <c r="A115" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C115" s="88">
+        <v>3.0</v>
+      </c>
+      <c r="D115" s="88">
+        <v>2.0</v>
+      </c>
+      <c r="E115" s="55"/>
+      <c r="F115" s="55"/>
+      <c r="G115" s="55"/>
+      <c r="H115" s="55"/>
+      <c r="I115" s="55"/>
+      <c r="J115" s="55"/>
+      <c r="K115" s="55"/>
+      <c r="L115" s="55"/>
+    </row>
+    <row r="116" ht="14.25" customHeight="1">
+      <c r="A116" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C116" s="76">
+        <f t="shared" ref="C116:D116" si="8">C115/5</f>
+        <v>0.6</v>
+      </c>
+      <c r="D116" s="76">
+        <f t="shared" si="8"/>
+        <v>0.4</v>
+      </c>
+      <c r="E116" s="55"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="55"/>
+      <c r="H116" s="55"/>
+      <c r="I116" s="55"/>
+      <c r="J116" s="55"/>
+      <c r="K116" s="55"/>
+      <c r="L116" s="55"/>
+    </row>
+    <row r="117" ht="14.25" customHeight="1">
+      <c r="A117" s="55"/>
+      <c r="B117" s="55"/>
+      <c r="C117" s="77"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="55"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="55"/>
+      <c r="I117" s="55"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="55"/>
+      <c r="L117" s="55"/>
+    </row>
+    <row r="118" ht="27.0" customHeight="1">
+      <c r="A118" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" s="55"/>
+      <c r="F118" s="55"/>
+      <c r="G118" s="55"/>
+      <c r="H118" s="55"/>
+      <c r="I118" s="55"/>
+      <c r="J118" s="55"/>
+      <c r="K118" s="55"/>
+      <c r="L118" s="55"/>
+    </row>
+    <row r="119" ht="14.25" customHeight="1">
+      <c r="A119" s="89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B119" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="C119" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="D119" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="E119" s="55"/>
+      <c r="F119" s="55"/>
+      <c r="G119" s="55"/>
+      <c r="H119" s="55"/>
+      <c r="I119" s="55"/>
+      <c r="J119" s="55"/>
+      <c r="K119" s="55"/>
+      <c r="L119" s="55"/>
+    </row>
+    <row r="120" ht="28.5" customHeight="1">
+      <c r="A120" s="93">
+        <v>1.0</v>
+      </c>
+      <c r="B120" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C120" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="D120" s="96"/>
+      <c r="E120" s="55"/>
+      <c r="F120" s="55"/>
+      <c r="G120" s="55"/>
+      <c r="H120" s="55"/>
+      <c r="I120" s="55"/>
+      <c r="J120" s="55"/>
+      <c r="K120" s="55"/>
+      <c r="L120" s="55"/>
+    </row>
+    <row r="121" ht="31.5" customHeight="1">
+      <c r="A121" s="67">
+        <v>2.0</v>
+      </c>
+      <c r="B121" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C121" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D121" s="72"/>
+      <c r="E121" s="55"/>
+      <c r="F121" s="55"/>
+      <c r="G121" s="55"/>
+      <c r="H121" s="55"/>
+      <c r="I121" s="55"/>
+      <c r="J121" s="55"/>
+      <c r="K121" s="55"/>
+      <c r="L121" s="55"/>
+    </row>
+    <row r="122" ht="30.0" customHeight="1">
+      <c r="A122" s="97">
+        <v>3.0</v>
+      </c>
+      <c r="B122" s="94" t="s">
+        <v>86</v>
+      </c>
+      <c r="C122" s="69"/>
+      <c r="D122" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="E122" s="55"/>
+      <c r="F122" s="55"/>
+      <c r="G122" s="55"/>
+      <c r="H122" s="55"/>
+      <c r="I122" s="55"/>
+      <c r="J122" s="55"/>
+      <c r="K122" s="55"/>
+      <c r="L122" s="55"/>
+    </row>
+    <row r="123" ht="14.25" customHeight="1">
+      <c r="A123" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C123" s="75">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$32:$C$34)</f>
+        <v>3</v>
+      </c>
+      <c r="D123" s="75">
+        <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$32:$D$34)</f>
+        <v>0</v>
+      </c>
+      <c r="E123" s="55"/>
+      <c r="F123" s="55"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="55"/>
+      <c r="I123" s="55"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="55"/>
+    </row>
+    <row r="124" ht="14.25" customHeight="1">
+      <c r="A124" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C124" s="76">
+        <f t="shared" ref="C124:D124" si="9">C123/3</f>
+        <v>1</v>
+      </c>
+      <c r="D124" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E124" s="55"/>
+      <c r="F124" s="55"/>
+      <c r="G124" s="55"/>
+      <c r="H124" s="55"/>
+      <c r="I124" s="55"/>
+      <c r="J124" s="55"/>
+      <c r="K124" s="55"/>
+      <c r="L124" s="55"/>
+    </row>
+    <row r="125" ht="14.25" customHeight="1">
+      <c r="A125" s="55"/>
+      <c r="B125" s="55"/>
+      <c r="C125" s="55"/>
+      <c r="D125" s="55"/>
+      <c r="E125" s="55"/>
+      <c r="F125" s="55"/>
+      <c r="G125" s="55"/>
+      <c r="H125" s="55"/>
+      <c r="I125" s="55"/>
+      <c r="J125" s="55"/>
+      <c r="K125" s="55"/>
+      <c r="L125" s="55"/>
+    </row>
+    <row r="126" ht="14.25" customHeight="1">
+      <c r="A126" s="55"/>
+      <c r="B126" s="55"/>
+      <c r="C126" s="55"/>
+      <c r="D126" s="55"/>
+      <c r="E126" s="55"/>
+      <c r="F126" s="55"/>
+      <c r="G126" s="55"/>
+      <c r="H126" s="55"/>
+      <c r="I126" s="55"/>
+      <c r="J126" s="55"/>
+      <c r="K126" s="55"/>
+      <c r="L126" s="55"/>
+    </row>
+    <row r="127" ht="14.25" customHeight="1">
+      <c r="A127" s="55"/>
+      <c r="B127" s="55"/>
+      <c r="C127" s="55"/>
+      <c r="D127" s="55"/>
+      <c r="E127" s="55"/>
+      <c r="F127" s="55"/>
+      <c r="G127" s="55"/>
+      <c r="H127" s="55"/>
+      <c r="I127" s="55"/>
+      <c r="J127" s="55"/>
+      <c r="K127" s="55"/>
+      <c r="L127" s="55"/>
+    </row>
+    <row r="128" ht="14.25" customHeight="1">
+      <c r="A128" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="D128" s="55"/>
+      <c r="E128" s="55"/>
+      <c r="F128" s="55"/>
+      <c r="G128" s="55"/>
+      <c r="H128" s="55"/>
+      <c r="I128" s="55"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="55"/>
+      <c r="L128" s="55"/>
+    </row>
+    <row r="129" ht="14.25" customHeight="1">
+      <c r="A129" s="55"/>
+      <c r="B129" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="C129" s="75">
+        <v>67.0</v>
+      </c>
+      <c r="D129" s="55"/>
+      <c r="E129" s="55"/>
+      <c r="F129" s="55"/>
+      <c r="G129" s="55"/>
+      <c r="H129" s="55"/>
+      <c r="I129" s="55"/>
+      <c r="J129" s="55"/>
+      <c r="K129" s="55"/>
+      <c r="L129" s="55"/>
+    </row>
+    <row r="130" ht="14.25" customHeight="1">
+      <c r="A130" s="55"/>
+      <c r="B130" s="99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C130" s="88">
+        <v>60.0</v>
+      </c>
+      <c r="D130" s="55"/>
+      <c r="E130" s="55"/>
+      <c r="F130" s="55"/>
+      <c r="G130" s="55"/>
+      <c r="H130" s="55"/>
+      <c r="I130" s="55"/>
+      <c r="J130" s="55"/>
+      <c r="K130" s="55"/>
+      <c r="L130" s="55"/>
+    </row>
+    <row r="131" ht="14.25" customHeight="1">
+      <c r="A131" s="55"/>
+      <c r="B131" s="99" t="s">
+        <v>83</v>
+      </c>
+      <c r="C131" s="75">
+        <v>100.0</v>
+      </c>
+      <c r="D131" s="55"/>
+      <c r="E131" s="55"/>
+      <c r="F131" s="55"/>
+      <c r="G131" s="55"/>
+      <c r="H131" s="55"/>
+      <c r="I131" s="55"/>
+      <c r="J131" s="55"/>
+      <c r="K131" s="55"/>
+      <c r="L131" s="55"/>
+    </row>
+    <row r="132" ht="14.25" customHeight="1">
+      <c r="A132" s="55"/>
+      <c r="B132" s="55"/>
+      <c r="C132" s="55"/>
+      <c r="D132" s="55"/>
+      <c r="E132" s="55"/>
+      <c r="F132" s="55"/>
+      <c r="G132" s="55"/>
+      <c r="H132" s="55"/>
+      <c r="I132" s="55"/>
+      <c r="J132" s="55"/>
+      <c r="K132" s="55"/>
+      <c r="L132" s="55"/>
+    </row>
+    <row r="133" ht="14.25" customHeight="1">
+      <c r="A133" s="55"/>
+      <c r="B133" s="55"/>
+      <c r="C133" s="55"/>
+      <c r="D133" s="55"/>
+      <c r="E133" s="55"/>
+      <c r="F133" s="55"/>
+      <c r="G133" s="55"/>
+      <c r="H133" s="55"/>
+      <c r="I133" s="55"/>
+      <c r="J133" s="55"/>
+      <c r="K133" s="55"/>
+      <c r="L133" s="55"/>
+    </row>
+    <row r="134" ht="14.25" customHeight="1">
+      <c r="A134" s="55"/>
+      <c r="B134" s="55"/>
+      <c r="C134" s="55"/>
+      <c r="D134" s="55"/>
+      <c r="E134" s="55"/>
+      <c r="F134" s="55"/>
+      <c r="G134" s="55"/>
+      <c r="H134" s="55"/>
+      <c r="I134" s="55"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="55"/>
+      <c r="L134" s="55"/>
+    </row>
+    <row r="135" ht="14.25" customHeight="1">
+      <c r="A135" s="55"/>
+      <c r="B135" s="55"/>
+      <c r="C135" s="55"/>
+      <c r="D135" s="55"/>
+      <c r="E135" s="55"/>
+      <c r="F135" s="55"/>
+      <c r="G135" s="55"/>
+      <c r="H135" s="55"/>
+      <c r="I135" s="55"/>
+      <c r="J135" s="55"/>
+      <c r="K135" s="55"/>
+      <c r="L135" s="55"/>
+    </row>
+    <row r="136" ht="14.25" customHeight="1">
+      <c r="A136" s="55"/>
+      <c r="B136" s="55"/>
+      <c r="C136" s="55"/>
+      <c r="D136" s="55"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
+    </row>
+    <row r="137" ht="14.25" customHeight="1">
+      <c r="A137" s="55"/>
+      <c r="B137" s="55"/>
+      <c r="C137" s="55"/>
+      <c r="D137" s="55"/>
+      <c r="E137" s="55"/>
+      <c r="F137" s="55"/>
+      <c r="G137" s="55"/>
+      <c r="H137" s="55"/>
+      <c r="I137" s="55"/>
+      <c r="J137" s="55"/>
+      <c r="K137" s="55"/>
+      <c r="L137" s="55"/>
+    </row>
     <row r="138" ht="14.25" customHeight="1"/>
     <row r="139" ht="14.25" customHeight="1"/>
     <row r="140" ht="14.25" customHeight="1"/>
@@ -3798,50 +5638,50 @@
     <row r="241" ht="14.25" customHeight="1"/>
     <row r="242" ht="14.25" customHeight="1"/>
     <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
     <row r="288" ht="15.75" customHeight="1"/>
     <row r="289" ht="15.75" customHeight="1"/>
     <row r="290" ht="15.75" customHeight="1"/>
@@ -4555,8 +6395,71 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="38">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A118:D118"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
@@ -4564,50 +6467,55 @@
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A71:B71"/>
   </mergeCells>
-  <conditionalFormatting sqref="A32:D34">
+  <conditionalFormatting sqref="A32:D34 A76:D78">
     <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(A32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
+  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34 C52:D60 C66:C70 C76:D78">
     <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
+  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34 C52:D60 C66:C70 C76:D78">
     <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
+  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34 C52:D60 C66:C70 C76:D78">
     <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
+  <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34 C52:D60 C66:C70 C76:D78">
     <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:D26">
+  <conditionalFormatting sqref="C22:D26 C66:D70">
     <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:D26">
+  <conditionalFormatting sqref="C22:D26 C66:D70">
     <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C32:D34">
+  <conditionalFormatting sqref="C32:D34 C76:D78">
     <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
     </cfRule>
@@ -4616,10 +6524,16 @@
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
-  <tableParts count="3">
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
+  <tableParts count="9">
+    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4637,78 +6551,162 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="52" t="s">
-        <v>89</v>
+      <c r="A1" s="100" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="100" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>91</v>
+      <c r="A2" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>93</v>
+      <c r="A3" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="101" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>95</v>
+      <c r="A4" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="103" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>97</v>
+      <c r="A5" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="103" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>99</v>
+      <c r="A6" s="103" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="103" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="55" t="s">
-        <v>101</v>
+      <c r="A7" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="103" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1"/>
     <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="104" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="100" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="100" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="105" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="103" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="103" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="103" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="104"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="104"/>
+    </row>
     <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="104" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="100" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="100" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="103" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="103" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="103" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="105" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="103" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="103" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1"/>
     <row r="27" ht="14.25" customHeight="1"/>
@@ -4902,9 +6900,9 @@
     <row r="215" ht="14.25" customHeight="1"/>
     <row r="216" ht="14.25" customHeight="1"/>
     <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
@@ -5682,9 +7680,6 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
